--- a/Result/profitability/9904.xlsx
+++ b/Result/profitability/9904.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.19</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0925</v>
+        <v>1.05125</v>
       </c>
       <c r="N2" t="n">
-        <v>23.33125</v>
+        <v>22.77625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.91</v>
+        <v>1.01625</v>
       </c>
       <c r="N3" t="n">
-        <v>23.13</v>
+        <v>22.5025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.855</v>
+        <v>1.05125</v>
       </c>
       <c r="N4" t="n">
-        <v>22.75625</v>
+        <v>22.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>-0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.845</v>
+        <v>1.375</v>
       </c>
       <c r="N5" t="n">
-        <v>22.93125</v>
+        <v>22.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6925000000000001</v>
+        <v>0.7325000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>23.07375</v>
+        <v>22.64375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>0.605</v>
+        <v>0.6737500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>23.295</v>
+        <v>22.92125</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58</v>
+        <v>0.68625</v>
       </c>
       <c r="N8" t="n">
-        <v>23.34875</v>
+        <v>23.08625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5625</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>23.7975</v>
@@ -1899,7 +1899,7 @@
         <v>0.89</v>
       </c>
       <c r="M12" t="n">
-        <v>0.61125</v>
+        <v>0.6112500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>25.355</v>
@@ -2026,7 +2026,7 @@
         <v>0.41</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6675</v>
+        <v>0.6675000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>24.69875</v>
@@ -9352,25 +9352,25 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4733</v>
+        <v>-8044</v>
       </c>
       <c r="J71" t="n">
-        <v>7585</v>
+        <v>-5192</v>
       </c>
       <c r="K71" t="n">
-        <v>5018</v>
+        <v>-7758</v>
       </c>
       <c r="L71" t="n">
-        <v>1.7</v>
+        <v>-2.63</v>
       </c>
       <c r="M71" t="n">
-        <v>1.15625</v>
+        <v>0.615</v>
       </c>
       <c r="N71" t="n">
         <v>24.52625</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -9382,22 +9382,22 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>1.66</v>
+        <v>-2.67</v>
       </c>
       <c r="X71" t="n">
-        <v>41.5</v>
+        <v>-66.75</v>
       </c>
       <c r="Y71" t="n">
         <v>-0.5999999999999979</v>
@@ -9406,10 +9406,10 @@
         <v>-0.02576212966938596</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.54</v>
+        <v>-3.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4655172413793105</v>
+        <v>-3.267241379310345</v>
       </c>
       <c r="AC71" t="n">
         <v>-1.109999999999999</v>
@@ -9418,10 +9418,10 @@
         <v>-0.04663865546218482</v>
       </c>
       <c r="AE71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率衰退</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9479,16 +9479,16 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3396</v>
+        <v>16173</v>
       </c>
       <c r="J72" t="n">
-        <v>6385</v>
+        <v>19162</v>
       </c>
       <c r="K72" t="n">
-        <v>3788</v>
+        <v>16565</v>
       </c>
       <c r="L72" t="n">
-        <v>1.29</v>
+        <v>5.62</v>
       </c>
       <c r="M72" t="n">
         <v>1.06</v>
@@ -9503,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -9515,16 +9515,16 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>-0.4099999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.2411764705882352</v>
+        <v>-3.136882129277567</v>
       </c>
       <c r="Y72" t="n">
         <v>0.7899999999999991</v>
@@ -9533,10 +9533,10 @@
         <v>0.03481710004407224</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.6499999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.3350515463917525</v>
+        <v>1.896907216494845</v>
       </c>
       <c r="AC72" t="n">
         <v>-1</v>
@@ -9545,10 +9545,10 @@
         <v>-0.04084967320261434</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG72" t="n">
         <v>1</v>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率衰退</t>
+          <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -9642,16 +9642,16 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.23</v>
+        <v>-4.56</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.1782945736434108</v>
+        <v>-0.8113879003558719</v>
       </c>
       <c r="Y73" t="n">
         <v>-0.4499999999999993</v>
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
         <v>115.1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>62998</v>
+      </c>
+      <c r="D75" t="n">
+        <v>50371</v>
+      </c>
+      <c r="E75" t="n">
+        <v>12627</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>848</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4764</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5612</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4753</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.02625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.118421052631579</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09485094850948517</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.612167300380228</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.650000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1167915381225211</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
